--- a/tests/urls/results.xlsx
+++ b/tests/urls/results.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -406,6 +406,9 @@
       <c r="B1" t="str">
         <v>Login visible?(yes/no)</v>
       </c>
+      <c r="C1" t="str">
+        <v>Login redirect (yes/no)</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -414,18 +417,46 @@
       <c r="B2" t="str">
         <v>YES</v>
       </c>
+      <c r="C2" t="str">
+        <v>YES</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>https://aapa.ltcrplus.com/</v>
       </c>
       <c r="B3" t="str">
+        <v>YES</v>
+      </c>
+      <c r="C3" t="str">
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>https://purdue.ltcrplus.com/?q=123</v>
+      </c>
+      <c r="B4" t="str">
+        <v>YES</v>
+      </c>
+      <c r="C4" t="str">
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>https://usu.ltcrplus.com/</v>
+      </c>
+      <c r="B5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="C5" t="str">
         <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/urls/results.xlsx
+++ b/tests/urls/results.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,7 +412,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://ltcrplus.com/</v>
+        <v>https://lsus.ltcrplus.com/</v>
       </c>
       <c r="B2" t="str">
         <v>YES</v>
@@ -423,7 +423,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://aapa.ltcrplus.com/</v>
+        <v>https://wscaa.ltcrplus.com/</v>
       </c>
       <c r="B3" t="str">
         <v>YES</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://purdue.ltcrplus.com/?q=123</v>
+        <v>https://umem.ltcrplus.com/</v>
       </c>
       <c r="B4" t="str">
         <v>YES</v>
@@ -445,18 +445,29 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://usu.ltcrplus.com/</v>
+        <v>https://elizc.ltcrplus.com/</v>
       </c>
       <c r="B5" t="str">
+        <v>YES</v>
+      </c>
+      <c r="C5" t="str">
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>https://iscpa.ltcrplus.com/</v>
+      </c>
+      <c r="B6" t="str">
         <v>NO</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/urls/results.xlsx
+++ b/tests/urls/results.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>URL</v>
       </c>
       <c r="B1" t="str">
-        <v>Login visible?(yes/no)</v>
+        <v>Button visible?(yes/no)</v>
       </c>
       <c r="C1" t="str">
         <v>Login redirect (yes/no)</v>
@@ -412,18 +412,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://lsus.ltcrplus.com/</v>
+        <v>https://iscpa.ltcrplus.com/</v>
       </c>
       <c r="B2" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="C2" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://wscaa.ltcrplus.com/</v>
+        <v>https://ltcrplus.com/</v>
       </c>
       <c r="B3" t="str">
         <v>YES</v>
@@ -434,40 +434,18 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://umem.ltcrplus.com/</v>
+        <v>https://aapa.ltcrplus.com/?abc</v>
       </c>
       <c r="B4" t="str">
         <v>YES</v>
       </c>
       <c r="C4" t="str">
         <v>YES</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://elizc.ltcrplus.com/</v>
-      </c>
-      <c r="B5" t="str">
-        <v>YES</v>
-      </c>
-      <c r="C5" t="str">
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>https://iscpa.ltcrplus.com/</v>
-      </c>
-      <c r="B6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="C6" t="str">
-        <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>